--- a/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Timéo est à la maison. Papa ouvre la porte du balcon. L'air sent le linge propre. Timéo reste avec l'adulte. Papa dit : on reste derrière la protection. Timéo pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Timéo pose les mains sur la protection. Il reste derrière la protection. Un pigeon roucoule. Timéo dit : papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Timéo est calme. Ils regardent le ciel. Plus tard, l'après-midi, papa revient. Timéo veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Timéo reste derrière la protection. L'adulte est là. C'est papa. Le vent est doux. Timéo compte les nuages. Un. Deux. Trois. Papa tient le bord de son gilet. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
+          <t>Timéo est à la maison. Papa ouvre la porte du balcon. L'air sent le linge propre. Timéo reste avec l'adulte. On reste derrière la protection. Timéo pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Timéo pose les mains sur la protection. Il reste derrière la protection. Un pigeon roucoule. Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Timéo est calme. Ils regardent le ciel. Plus tard, l'après-midi, papa revient. Timéo veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Timéo reste derrière la protection. L'adulte est là. C'est papa. Le vent est doux. Timéo compte les nuages. Un. Deux. Trois. Papa tient le bord de son gilet. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Timéo est à la maison. Papa ouvre la porte du balcon. L'air sent le linge propre. Timéo reste avec l'adulte.
+papa|On reste derrière la protection.
+narrateur|Timéo pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Timéo pose les mains sur la protection. Il reste derrière la protection. Un pigeon roucoule.
+enfant-m|Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Timéo est calme.
+narrateur|Ils regardent le ciel. Plus tard, l'après-midi, papa revient. Timéo veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Timéo reste derrière la protection. L'adulte est là. C'est papa. Le vent est doux. Timéo compte les nuages. Un. Deux. Trois. Papa tient le bord de son gilet. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Timéo est au balcon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Timéo a les pieds au sol. Il est derrière la protection. Papa, l'adulte, est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Timéo et papa rentrent. Les pieds restent au sol.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Ils regardent le ciel. Plus tard, l'après-midi, papa revient. Timéo veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Timéo reste derrière la protection. L'adulte est là. C'est papa. Le vent est doux. Timéo compte les nuages. Un. Deux. Trois. Papa tient le bord de son gilet. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Timéo est au balcon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Timéo a les pieds au sol. Il est derrière la protection. Papa, l'adulte, est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1859,7 @@
           <t>narrateur|Timéo et papa rentrent. Les pieds restent au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timéo au balcon avec papa</t>
+          <t>Le drap de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un drap blanc claque. Victorino va au balcon avec papa. Un pigeon roucoule. L'après-midi, ils reviennent. Pieds au sol, derrière la protection.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Timéo est à la maison. Papa ouvre la porte du balcon. L'air sent le linge propre. Timéo reste avec l'adulte. On reste derrière la protection. Timéo pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Timéo pose les mains sur la protection. Il reste derrière la protection. Un pigeon roucoule. Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Timéo est calme. Ils regardent le ciel. Plus tard, l'après-midi, papa revient. Timéo veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Timéo reste derrière la protection. L'adulte est là. C'est papa. Le vent est doux. Timéo compte les nuages. Un. Deux. Trois. Papa tient le bord de son gilet. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
+          <t>Un drap blanc claque, tout loin. Il sent le savon, encore frais. Le vent le gonfle, puis le lâche. Une pince en bois tient le bord. Ça sent le linge propre, dans la maison. Le soleil fait un carré sur le tapis. Une pince en bois attend près du panier. Tu as senti le linge, Victorino ? Oui, papa. Ça sent le propre. Le drap sèche au vent. En ce moment, papa ouvre la porte. L'air sent le linge, plus fort. Victorino reste avec l'adulte. On reste derrière la protection. D'accord, papa. Victorino pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Victorino pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un pigeon roucoule, tout bas. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Victorino est calme. Ils regardent le ciel. Tu as fini de regarder le pigeon ? Il est encore là. Alors on reste. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Plus tard, l'après-midi, papa revient. Victorino veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Victorino reste derrière la protection. L'adulte est près de lui. C'est papa. Le vent est doux. Victorino compte les nuages. Un. Deux. Trois. Tu comptes bien. Bravo. Papa tient le bord de son gilet. On rentre, maintenant ? Oui, papa. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Timéo est à la maison. Papa ouvre la porte du balcon. L'air sent le linge propre. Timéo reste avec l'adulte.
+          <t>narrateur|Un drap blanc claque, tout loin.
+narrateur|Il sent le savon, encore frais.
+narrateur|Le vent le gonfle, puis le lâche.
+narrateur|Une pince en bois tient le bord.
+narrateur|Ça sent le linge propre, dans la maison.
+narrateur|Le soleil fait un carré sur le tapis.
+narrateur|Une pince en bois attend près du panier.
+papa|Tu as senti le linge, Victorino ?
+enfant-m|Oui, papa.
+enfant-m|Ça sent le propre.
+papa|Le drap sèche au vent.
+narrateur|En ce moment, papa ouvre la porte.
+narrateur|L'air sent le linge, plus fort.
+narrateur|Victorino reste avec l'adulte.
 papa|On reste derrière la protection.
-narrateur|Timéo pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Timéo pose les mains sur la protection. Il reste derrière la protection. Un pigeon roucoule.
-enfant-m|Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Timéo est calme.
-narrateur|Ils regardent le ciel. Plus tard, l'après-midi, papa revient. Timéo veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Timéo reste derrière la protection. L'adulte est là. C'est papa. Le vent est doux. Timéo compte les nuages. Un. Deux. Trois. Papa tient le bord de son gilet. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
+enfant-m|D'accord, papa.
+narrateur|Victorino pose les pieds au sol.
+narrateur|Les pieds restent au sol.
+narrateur|Il sent le bois sous les chaussettes.
+narrateur|La protection est devant lui.
+narrateur|Victorino pose les mains sur la protection.
+narrateur|Il reste derrière la protection.
+papa|Bravo.
+papa|Tes pieds sont au sol.
+narrateur|Un pigeon roucoule, tout bas.
+enfant-m|Papa, l'oiseau.
+papa|Je l'entends.
+papa|On le regarde ici, avec moi.
+narrateur|Papa est près de lui.
+narrateur|Parce que les pieds sont au sol, Victorino est calme.
+narrateur|Ils regardent le ciel.
+papa|Tu as fini de regarder le pigeon ?
+enfant-m|Il est encore là.
+papa|Alors on reste.
+papa|Derrière la protection.
+enfant-m|Pieds au sol.
+papa|Oui.
+papa|C'est du bon travail.
+narrateur|Plus tard, l'après-midi, papa revient.
+narrateur|Victorino veut revoir le pigeon.
+narrateur|Ils vont au balcon encore.
+narrateur|Les pieds restent au sol.
+narrateur|Victorino reste derrière la protection.
+narrateur|L'adulte est près de lui.
+narrateur|C'est papa.
+narrateur|Le vent est doux.
+narrateur|Victorino compte les nuages.
+enfant-m|Un.
+enfant-m|Deux.
+enfant-m|Trois.
+papa|Tu comptes bien.
+papa|Bravo.
+narrateur|Papa tient le bord de son gilet.
+papa|On rentre, maintenant ?
+enfant-m|Oui, papa.
+narrateur|Le soir, ils rentrent.
+narrateur|Les pieds restent au sol jusqu'à la porte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>linge,oiseau</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Timéo est au balcon. Que fait-il ?</t>
+          <t>Victorino est au balcon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Timéo est au balcon. Que fait-il ?</t>
+          <t>narrateur|Victorino est au balcon.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Timéo a les pieds au sol. Il est derrière la protection. Papa, l'adulte, est là.</t>
+          <t>Victorino a les pieds au sol. Il est derrière la protection. Tu es avec l'adulte. Bravo, Victorino. Pieds au sol. Avec papa. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1749,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Timéo a les pieds au sol. Il est derrière la protection. Papa, l'adulte, est là.</t>
+          <t>narrateur|Victorino a les pieds au sol.
+narrateur|Il est derrière la protection.
+papa|Tu es avec l'adulte.
+papa|Bravo, Victorino.
+enfant-m|Pieds au sol.
+enfant-m|Avec papa.
+papa|Oui.
+papa|C'est du bon travail.
+papa|Tu restes derrière la protection ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Timéo et papa rentrent. Les pieds restent au sol.</t>
+          <t>Victorino et papa rentrent. Les pieds restent au sol. Le drap blanc est plus sec. On rentre le linge plus tard. Tu as les pieds au sol, encore. Le pigeon a chanté. On l'a écouté ensemble. Derrière la protection. Bravo. Tu veux compter encore un nuage ? Quatre. Bravo. Le tapis est chaud sous les pieds.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1856,7 +1930,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Timéo et papa rentrent. Les pieds restent au sol.</t>
+          <t>narrateur|Victorino et papa rentrent.
+narrateur|Les pieds restent au sol.
+narrateur|Le drap blanc est plus sec.
+papa|On rentre le linge plus tard.
+papa|Tu as les pieds au sol, encore.
+enfant-m|Le pigeon a chanté.
+papa|On l'a écouté ensemble.
+papa|Derrière la protection.
+papa|Bravo.
+papa|Tu veux compter encore un nuage ?
+enfant-m|Quatre.
+papa|Bravo.
+narrateur|Le tapis est chaud sous les pieds.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1884,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le matin, le pigeon. L'après-midi, les nuages. Pieds au sol. Bravo. Tu as fait du bon travail. Le drap blanc ne claque plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2024,7 +2110,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le matin, le pigeon.
+enfant-m|L'après-midi, les nuages.
+papa|Pieds au sol.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le drap blanc ne claque plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2046,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un drap blanc claque, tout loin. Il sent le savon, encore frais. Le vent le gonfle, puis le lâche. Une pince en bois tient le bord. Ça sent le linge propre, dans la maison. Le soleil fait un carré sur le tapis. Une pince en bois attend près du panier. Tu as senti le linge, Victorino ? Oui, papa. Ça sent le propre. Le drap sèche au vent. En ce moment, papa ouvre la porte. L'air sent le linge, plus fort. Victorino reste avec l'adulte. On reste derrière la protection. D'accord, papa. Victorino pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Victorino pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un pigeon roucoule, tout bas. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Victorino est calme. Ils regardent le ciel. Tu as fini de regarder le pigeon ? Il est encore là. Alors on reste. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Plus tard, l'après-midi, papa revient. Victorino veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Victorino reste derrière la protection. L'adulte est près de lui. C'est papa. Le vent est doux. Victorino compte les nuages. Un. Deux. Trois. Tu comptes bien. Bravo. Papa tient le bord de son gilet. On rentre, maintenant ? Oui, papa. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
+          <t>Un drap blanc claque, tout loin. Il sent le savon, encore frais. Le vent le gonfle, puis le lâche. Une pince en bois tient le bord. Ça sent le linge propre, dans la maison. Le soleil fait un carré sur le tapis. Une pince en bois attend près du panier. Tu as senti le linge, Victorino ? Oui, papa. Ça sent le propre. Le drap sèche au vent. En ce moment, papa ouvre la porte. L'air sent le linge, plus fort. Victorino reste avec l'adulte. On reste derrière la protection. D'accord, papa. Victorino pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Victorino pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un pigeon roucoule, tout bas. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Victorino est calme. Ils regardent le ciel. Tu as fini de regarder le pigeon ? Il est encore là. Alors on reste. Derrière la protection. Pieds au sol. Oui. Plus tard, l'après-midi, papa revient. Victorino veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Victorino reste derrière la protection. L'adulte est près de lui. C'est papa. Le vent est doux. Victorino compte les nuages. Un. Deux. Trois. Tu comptes bien. Bravo. Papa tient le bord de son gilet. On rentre, maintenant ? Oui, papa. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Timéo est à la maison. Papa ouvre la porte du balcon. L'air sent le linge propre. Timéo reste avec l'adulte. Papa dit : on reste derrière la protection. Timéo pose les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Timéo pose les mains sur la protection. Il reste derrière la protection. Un pigeon roucoule. Timéo dit : papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Timéo est calme. Ils regardent le ciel. Plus tard, l'après-midi, papa revient. Timéo veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Timéo reste derrière la protection. L'adulte est là. C'est papa. Le vent est doux. Timéo compte les nuages. Un. Deux. Trois. Papa tient le bord de son gilet. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un drap blanc claque, tout loin. Il sent le savon, encore frais. Le vent le gonfle, puis le lâche. Une pince en bois tient le bord. Ça sent le linge propre, dans la maison. Le soleil fait un carré sur le tapis. Une pince en bois attend près du panier. Tu as senti le linge, Victorino ? Oui, papa. Ça sent le propre. Le drap sèche au vent. En ce moment, papa ouvre la porte. L'air sent le linge, plus fort. Victorino reste avec l'adulte. On reste derrière la protection. D'accord, papa. Victorino pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Victorino pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un pigeon roucoule, tout bas. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Victorino est calme. Ils regardent le ciel. Tu as fini de regarder le pigeon ? Il est encore là. Alors on reste. Derrière la protection. Pieds au sol. Oui. Plus tard, l'après-midi, papa revient. Victorino veut revoir le pigeon. Ils vont au balcon encore. Les pieds restent au sol. Victorino reste derrière la protection. L'adulte est près de lui. C'est papa. Le vent est doux. Victorino compte les nuages. Un. Deux. Trois. Tu comptes bien. Bravo. Papa tient le bord de son gilet. On rentre, maintenant ? Oui, papa. Le soir, ils rentrent. Les pieds restent au sol jusqu'à la porte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 papa|Derrière la protection.
 enfant-m|Pieds au sol.
 papa|Oui.
-papa|C'est du bon travail.
 narrateur|Plus tard, l'après-midi, papa revient.
 narrateur|Victorino veut revoir le pigeon.
 narrateur|Ils vont au balcon encore.
@@ -1417,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Timéo est au balcon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino est au balcon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1575,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a les pieds au sol. Il est derrière la protection. Tu es avec l'adulte. Bravo, Victorino. Pieds au sol. Avec papa. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, papa.</t>
+          <t>Victorino a les pieds au sol. Il est derrière la protection. Tu es avec l'adulte. Bravo, Victorino. Pieds au sol. Avec papa. Oui. Tu restes derrière la protection ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Timéo a les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Il est derrière la protection. Papa, l'adulte, est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a les pieds au sol. Il est derrière la protection. Tu es avec l'adulte. Bravo, Victorino. Pieds au sol. Avec papa. Oui. Tu restes derrière la protection ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,12 +1754,10 @@
 enfant-m|Pieds au sol.
 enfant-m|Avec papa.
 papa|Oui.
-papa|C'est du bon travail.
 papa|Tu restes derrière la protection ?
 enfant-m|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Timéo et papa rentrent. Les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; restent au sol.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino et papa rentrent. Les pieds restent au sol. Le drap blanc est plus sec. On rentre le linge plus tard. Tu as les pieds au sol, encore. Le pigeon a chanté. On l'a écouté ensemble. Derrière la protection. Bravo. Tu veux compter encore un nuage ? Quatre. Bravo. Le tapis est chaud sous les pieds.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,7 +1941,6 @@
 narrateur|Le tapis est chaud sous les pieds.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1970,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le matin, le pigeon. L'après-midi, les nuages. Pieds au sol. Bravo. Tu as fait du bon travail. Le drap blanc ne claque plus. L'histoire est finie.</t>
+          <t>Le matin, le pigeon. L'après-midi, les nuages. Pieds au sol. Bravo. Le drap blanc ne claque plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le matin, le pigeon. L'après-midi, les nuages. Pieds au sol. Bravo. Le drap blanc ne claque plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2109,9 @@
 enfant-m|L'après-midi, les nuages.
 papa|Pieds au sol.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le drap blanc ne claque plus.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le drap blanc ne claque plus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timéo, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
